--- a/examples/HFP_morgan.xlsx
+++ b/examples/HFP_morgan.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,60 +431,70 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>gross earnings</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>months worked</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>other inc</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>net inv</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Roth conv fixed</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -516,18 +526,25 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>6500</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>4000</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -557,18 +574,25 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>6500</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>4000</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -598,18 +622,25 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>6500</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>4000</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -639,18 +670,25 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>7000</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>4000</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -680,18 +718,25 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>7000</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>4000</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -729,10 +774,17 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -770,10 +822,17 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -811,10 +870,17 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -852,10 +918,17 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -893,10 +966,17 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -934,10 +1014,17 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -975,10 +1062,17 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1016,10 +1110,17 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1057,10 +1158,17 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1098,10 +1206,17 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1139,10 +1254,17 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1180,10 +1302,17 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1221,10 +1350,17 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1262,10 +1398,17 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1303,10 +1446,17 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1344,10 +1494,17 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1385,10 +1542,17 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1426,10 +1590,17 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1467,10 +1638,17 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1508,10 +1686,17 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1549,10 +1734,17 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1590,10 +1782,17 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1631,10 +1830,17 @@
       <c r="K29" t="n">
         <v>0</v>
       </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1672,10 +1878,17 @@
       <c r="K30" t="n">
         <v>0</v>
       </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="n">
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1713,10 +1926,17 @@
       <c r="K31" t="n">
         <v>0</v>
       </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31" t="n">
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1754,10 +1974,17 @@
       <c r="K32" t="n">
         <v>0</v>
       </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1795,10 +2022,17 @@
       <c r="K33" t="n">
         <v>0</v>
       </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1836,10 +2070,17 @@
       <c r="K34" t="n">
         <v>0</v>
       </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="n">
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1877,10 +2118,17 @@
       <c r="K35" t="n">
         <v>0</v>
       </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="n">
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1918,10 +2166,17 @@
       <c r="K36" t="n">
         <v>0</v>
       </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1959,10 +2214,17 @@
       <c r="K37" t="n">
         <v>0</v>
       </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2000,10 +2262,17 @@
       <c r="K38" t="n">
         <v>0</v>
       </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N38" t="n">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2041,10 +2310,17 @@
       <c r="K39" t="n">
         <v>0</v>
       </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="n">
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2082,10 +2358,17 @@
       <c r="K40" t="n">
         <v>0</v>
       </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="N40" t="n">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2123,10 +2406,17 @@
       <c r="K41" t="n">
         <v>0</v>
       </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="N41" t="n">
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2164,10 +2454,17 @@
       <c r="K42" t="n">
         <v>0</v>
       </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
-      <c r="N42" t="n">
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2205,10 +2502,17 @@
       <c r="K43" t="n">
         <v>0</v>
       </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
-      <c r="N43" t="n">
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2246,10 +2550,17 @@
       <c r="K44" t="n">
         <v>0</v>
       </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
-      <c r="N44" t="n">
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2266,10 +2577,6 @@
   </sheetPr>
   <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/examples/HFP_morgan.xlsx
+++ b/examples/HFP_morgan.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,70 +431,60 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>gross earnings</t>
+          <t>other inc</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>months worked</t>
+          <t>net inv</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>other inc</t>
+          <t>taxable ctrb</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>net inv</t>
+          <t>401k ctrb</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>taxable ctrb</t>
+          <t>Roth 401k ctrb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>401k ctrb</t>
+          <t>IRA ctrb</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Roth 401k ctrb</t>
+          <t>Roth IRA ctrb</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>IRA ctrb</t>
+          <t>HSA ctrb</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Roth IRA ctrb</t>
+          <t>Roth conv</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>HSA ctrb</t>
+          <t>Roth conv fixed</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Roth conv</t>
+          <t>QCD</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
-        <is>
-          <t>Roth conv fixed</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>QCD</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -526,25 +516,18 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="K2" t="n">
-        <v>6500</v>
-      </c>
-      <c r="L2" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -574,25 +557,18 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="K3" t="n">
-        <v>6500</v>
-      </c>
-      <c r="L3" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -622,25 +598,18 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="K4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="L4" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -670,25 +639,18 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="K5" t="n">
-        <v>7000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -718,25 +680,18 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="K6" t="n">
-        <v>7000</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -774,17 +729,10 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="N7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -822,17 +770,10 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="N8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -870,17 +811,10 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="N9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -918,17 +852,10 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -966,17 +893,10 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1014,17 +934,10 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1062,17 +975,10 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1110,17 +1016,10 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1158,17 +1057,10 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1206,17 +1098,10 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1254,17 +1139,10 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1302,17 +1180,10 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1350,17 +1221,10 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1398,17 +1262,10 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="N20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1446,17 +1303,10 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1494,17 +1344,10 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="N22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1542,17 +1385,10 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="N23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1590,17 +1426,10 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="N24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1638,17 +1467,10 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1686,17 +1508,10 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
+      <c r="N26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1734,17 +1549,10 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="N27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1782,17 +1590,10 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
+      <c r="N28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1830,17 +1631,10 @@
       <c r="K29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
+      <c r="N29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1878,17 +1672,10 @@
       <c r="K30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="N30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1926,17 +1713,10 @@
       <c r="K31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="N31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1974,17 +1754,10 @@
       <c r="K32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="N32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2022,17 +1795,10 @@
       <c r="K33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
+      <c r="N33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2070,17 +1836,10 @@
       <c r="K34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
+      <c r="N34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2118,17 +1877,10 @@
       <c r="K35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
+      <c r="N35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2166,17 +1918,10 @@
       <c r="K36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
+      <c r="N36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2214,17 +1959,10 @@
       <c r="K37" t="n">
         <v>0</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
+      <c r="N37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2262,17 +2000,10 @@
       <c r="K38" t="n">
         <v>0</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
+      <c r="N38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2310,17 +2041,10 @@
       <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
+      <c r="N39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2358,17 +2082,10 @@
       <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
+      <c r="N40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2406,17 +2123,10 @@
       <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
+      <c r="N41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2454,17 +2164,10 @@
       <c r="K42" t="n">
         <v>0</v>
       </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
+      <c r="N42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2502,17 +2205,10 @@
       <c r="K43" t="n">
         <v>0</v>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
+      <c r="N43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2550,17 +2246,10 @@
       <c r="K44" t="n">
         <v>0</v>
       </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
+      <c r="N44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2577,6 +2266,10 @@
   </sheetPr>
   <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
